--- a/docs/downloads/Peterborough.xlsx
+++ b/docs/downloads/Peterborough.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nash</t>
+          <t>Safar-parent</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rnpnash@bell.net</t>
+          <t>ashleysafar@outlook.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Debra</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Safar-parent</t>
+          <t>Weichel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ashleysafar@outlook.com</t>
+          <t>debweichel776@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Shaughnessy</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mshaughnessy@sympatico.ca</t>
+          <t>phil.adams111@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Debra</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Weichel</t>
+          <t>Mosienko</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>debweichel776@gmail.com</t>
+          <t>lori.mosienko@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Redhead</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>phil.adams111@gmail.com</t>
+          <t>sredhead1967@yahoo.ca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mosienko</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>lori.mosienko@gmail.com</t>
+          <t>sabrina.kim.walker@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Redhead</t>
+          <t>Stefanski</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sredhead1967@yahoo.ca</t>
+          <t>stefanskilisa@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Vautour</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>sabrina.kim.walker@gmail.com</t>
+          <t>vautour.lyn@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Clem</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Stefanski</t>
+          <t>Garvey</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>stefanskilisa@gmail.com</t>
+          <t>beleaf62@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Deanne</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vautour</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>vautour.lyn@gmail.com</t>
+          <t>deanne_graham@live.ca</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clinton</t>
+          <t>Marlene</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Baillie</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>clinton.smith007@gmail.com</t>
+          <t>marlenebaillie@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clem</t>
+          <t>WENDY</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Garvey</t>
+          <t>Couper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>beleaf62@gmail.com</t>
+          <t>wendycouper@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deanne</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Kayser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>deanne_graham@live.ca</t>
+          <t>rkayser1010@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marlene</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baillie</t>
+          <t>Corso</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>marlenebaillie@gmail.com</t>
+          <t>heathercorso@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WENDY</t>
+          <t>Corinne</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Couper</t>
+          <t>Jenden-Selway</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wendycouper@gmail.com</t>
+          <t>jendenselwayca@aol.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kayser</t>
+          <t>Fellion</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>rkayser1010@gmail.com</t>
+          <t>heatherfellion@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Cheryl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Corso</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>heathercorso@gmail.com</t>
+          <t>cherylchristie44@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Corinne</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jenden-Selway</t>
+          <t>Szabolcs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jendenselwayca@aol.com</t>
+          <t>cathyszab@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Dhruv</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fellion</t>
+          <t>Mittal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>heatherfellion@gmail.com</t>
+          <t>mittaldhruv99@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cheryl</t>
+          <t>Sadaf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Hussain</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>cherylchristie44@gmail.com</t>
+          <t>sadaf18@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Szabolcs</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>cathyszab@gmail.com</t>
+          <t>brittany_avon@ymail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dhruv</t>
+          <t>Kylie</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mittal</t>
+          <t>Morrison</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>mittaldhruv99@gmail.com</t>
+          <t>kylierosemorrison@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sadaf</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hussain</t>
+          <t>Merpaw</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sadaf18@gmail.com</t>
+          <t>merpaw483@bell.net</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>brittany_avon@ymail.com</t>
+          <t>spacebuffalo1@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kylie</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Morrison</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kylierosemorrison@gmail.com</t>
+          <t>katie.wright1954@gmail.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Angelica</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Merpaw</t>
+          <t>Jimenez santamaria</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>merpaw483@bell.net</t>
+          <t>angelicapmp@yahoo.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Duggan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>spacebuffalo1@gmail.com</t>
+          <t>stephduggan55@hotmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Micks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>katie.wright1954@gmail.com</t>
+          <t>micksfamily5@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jimenez santamaria</t>
+          <t>MacDowall</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>angelicapmp@yahoo.com</t>
+          <t>dheliam26@icloud.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Duggan</t>
+          <t>Chamberlain</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>stephduggan55@hotmail.com</t>
+          <t>pamelachamberlain12@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Micks</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>micksfamily5@gmail.com</t>
+          <t>shannonkelly@live.ca</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MacDowall</t>
+          <t>Hunt</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dheliam26@icloud.com</t>
+          <t>rjd4hunt@hotmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Jordyn</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Chamberlain</t>
+          <t>GEROLAMY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>pamelachamberlain12@gmail.com</t>
+          <t>j_gerolamy@live.ca</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Hawksworth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>shannonkelly@live.ca</t>
+          <t>ladydihawk@sympatico.ca</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>rjd4hunt@hotmail.com</t>
+          <t>tomtaylor74367@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jordyn</t>
+          <t>Kristin</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEROLAMY</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>j_gerolamy@live.ca</t>
+          <t>kclark230@hmail.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Sonya</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hawksworth</t>
+          <t>Hardman</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ladydihawk@sympatico.ca</t>
+          <t>sonyahardman@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>tomtaylor74367@gmail.com</t>
+          <t>onthebeach644@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kristin</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Moldaver</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kclark230@hmail.com</t>
+          <t>maureen.reisch@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sonya</t>
+          <t>Shavaughn</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hardman</t>
+          <t>Soraine</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sonyahardman@gmail.com</t>
+          <t>shavaughn.soraine@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>SUMMERS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>onthebeach644@gmail.com</t>
+          <t>adamsummerspt@gmail.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Moldaver</t>
+          <t>Whalen</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>maureen.reisch@gmail.com</t>
+          <t>karenwhalen1955@gmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Shavaughn</t>
+          <t>Jennelle</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Soraine</t>
+          <t>Cullen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>shavaughn.soraine@gmail.com</t>
+          <t>jcullen@compasselc.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SUMMERS</t>
+          <t>Foden</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>adamsummerspt@gmail.com</t>
+          <t>slfoden@icloud.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Whalen</t>
+          <t>Crowley</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>karenwhalen1955@gmail.com</t>
+          <t>albertzitacrowley@gmail.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>scott</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Westropp</t>
+          <t>laing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>bwestropp@cogeco.ca</t>
+          <t>buster6150@hotmail.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jennelle</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cullen</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>jcullen@compasselc.com</t>
+          <t>shar.kell.clar@gmail.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Foden</t>
+          <t>Mcmaster</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>slfoden@icloud.com</t>
+          <t>cathymcmaster58@gmail.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Kimber</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Crowley</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>albertzitacrowley@gmail.com</t>
+          <t>bkbell94@yahoo.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>scott</t>
+          <t>Rachele</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>laing</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>buster6150@hotmail.com</t>
+          <t>rachelebell96@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Titus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>shar.kell.clar@gmail.com</t>
+          <t>99silverado@sympatico.ca</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Mcmaster</t>
+          <t>Tsafaridis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>cathymcmaster58@gmail.com</t>
+          <t>safarimag69@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kimber</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Greenfield</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>bkbell94@yahoo.com</t>
+          <t>melanie.greenfield8@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rachele</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Fulcher</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rachelebell96@gmail.com</t>
+          <t>kim9fulcher@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Titus</t>
+          <t>Bolton</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>99silverado@sympatico.ca</t>
+          <t>tinaebolton@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,17 +2349,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Denisa</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tsafaridis</t>
+          <t>Reiz</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>safarimag69@gmail.com</t>
+          <t>adeelight779@gmail.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2371,17 +2371,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Carmelina</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Greenfield</t>
+          <t>Tamburini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>melanie.greenfield8@gmail.com</t>
+          <t>carmelinaeliseo@hotmail.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2393,17 +2393,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Zaa</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fulcher</t>
+          <t>Nkweta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>kim9fulcher@gmail.com</t>
+          <t>nkwetaz@gmail.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Tracey</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Manns</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>tinaebolton@gmail.com</t>
+          <t>tracey.manns@gmail.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2437,17 +2437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Denisa</t>
+          <t>Aditya</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Reiz</t>
+          <t>Girdhar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>adeelight779@gmail.com</t>
+          <t>girdhar0820@gmail.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2459,152 +2459,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Carmelina</t>
+          <t>Madelyne</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tamburini</t>
+          <t>Raja</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>carmelinaeliseo@hotmail.com</t>
+          <t>madelyneraja@gmail.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Zaa</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Nkweta</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>nkwetaz@gmail.com</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Tracey</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Manns</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>tracey.manns@gmail.com</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Donna</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Bowmer</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>djbowmer1@gmail.com</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Aditya</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Girdhar</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>girdhar0820@gmail.com</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Madelyne</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Raja</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>madelyneraja@gmail.com</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>peterborough@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Heysel</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>pheysel@gmail.com</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
         <is>
           <t>peterborough@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Peterborough.xlsx
+++ b/docs/downloads/Peterborough.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Safar-parent</t>
+          <t>Carveth</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ashleysafar@outlook.com</t>
+          <t>w.carveth65@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Debra</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Weichel</t>
+          <t>Winn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>debweichel776@gmail.com</t>
+          <t>r.winn@sympatico.ca</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Phil</t>
+          <t>Allison</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Seiderer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>phil.adams111@gmail.com</t>
+          <t>allison@livingwellhme.ca</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mosienko</t>
+          <t>Marcotte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>lori.mosienko@gmail.com</t>
+          <t>nancyjmarcotte@hotmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Redhead</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sredhead1967@yahoo.ca</t>
+          <t>samanthajaner@yahoo.ca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Walker</t>
+          <t>Healey</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sabrina.kim.walker@gmail.com</t>
+          <t>elizabethhealey99@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Stefanski</t>
+          <t>Hussey</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>stefanskilisa@gmail.com</t>
+          <t>al@thebikegarage.ca</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lynne</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vautour</t>
+          <t>Bitonte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>vautour.lyn@gmail.com</t>
+          <t>yogasue@gmail.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clem</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Garvey</t>
+          <t>Miljevic</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>beleaf62@gmail.com</t>
+          <t>kkoroscik@yahoo.ca</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Deanne</t>
+          <t>Denise</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Graham</t>
+          <t>Hicks-leal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>deanne_graham@live.ca</t>
+          <t>dhicksleal@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marlene</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baillie</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>marlenebaillie@gmail.com</t>
+          <t>blackknightwayne@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WENDY</t>
+          <t>Ashley</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Couper</t>
+          <t>Safar-parent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>wendycouper@gmail.com</t>
+          <t>ashleysafar@outlook.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kayser</t>
+          <t>Labelle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rkayser1010@gmail.com</t>
+          <t>sjlacoste7@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corso</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>heathercorso@gmail.com</t>
+          <t>hardy.kraft13@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Corinne</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jenden-Selway</t>
+          <t>Mitchell</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jendenselwayca@aol.com</t>
+          <t>cmil_98@yahoo.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Allie</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fellion</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>heatherfellion@gmail.com</t>
+          <t>alliemaryanna@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cheryl</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Purvis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>cherylchristie44@gmail.com</t>
+          <t>drjpurvis@rheumdoc.ca</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Catherine</t>
+          <t>Brian</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Szabolcs</t>
+          <t>Fowler</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cathyszab@gmail.com</t>
+          <t>bbfowler8@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dhruv</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mittal</t>
+          <t>Schauber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mittaldhruv99@gmail.com</t>
+          <t>pschauber@hotmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sadaf</t>
+          <t>Jon</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hussain</t>
+          <t>Bye</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sadaf18@gmail.com</t>
+          <t>jbye@hotmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Corey</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Leeming</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>brittany_avon@ymail.com</t>
+          <t>redbombers@hotmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kylie</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Morrison</t>
+          <t>Kassil</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kylierosemorrison@gmail.com</t>
+          <t>lindalpd68@gmail.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Merpaw</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>merpaw483@bell.net</t>
+          <t>reeniemacd@icloud.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Charmayne</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Kocsis</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>spacebuffalo1@gmail.com</t>
+          <t>charmayneot@yahoo.ca</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Patti</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>katie.wright1954@gmail.com</t>
+          <t>patti-k@hotmail.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Angelica</t>
+          <t>Debra</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jimenez santamaria</t>
+          <t>Weichel</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>angelicapmp@yahoo.com</t>
+          <t>debweichel776@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Duggan</t>
+          <t>Keane</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>stephduggan55@hotmail.com</t>
+          <t>keanepb@hotmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Micks</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>micksfamily5@gmail.com</t>
+          <t>barbmart12@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MacDowall</t>
+          <t>Tomaszewski</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>dheliam26@icloud.com</t>
+          <t>iamcanadn@rogers.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Chamberlain</t>
+          <t>Sloukji</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pamelachamberlain12@gmail.com</t>
+          <t>sam.sloukji@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Jodi</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Turnbull</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>shannonkelly@live.ca</t>
+          <t>joditurnbull@live.ca</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Jackie</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hunt</t>
+          <t>Muldoon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rjd4hunt@hotmail.com</t>
+          <t>jackie.muldoon@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jordyn</t>
+          <t>Alivia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEROLAMY</t>
+          <t>Powers</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>j_gerolamy@live.ca</t>
+          <t>alivia@powersfamily.ca</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hawksworth</t>
+          <t>Weichel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ladydihawk@sympatico.ca</t>
+          <t>tom.weichel@bellvedt.ca</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Joan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>tomtaylor74367@gmail.com</t>
+          <t>joanandlilah@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kristin</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Beard</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>kclark230@hmail.com</t>
+          <t>dbeard@globalpointenergy.ca</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sonya</t>
+          <t>Marianne</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hardman</t>
+          <t>Sharkey</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sonyahardman@gmail.com</t>
+          <t>mariannesharkey@gmail.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Sukornyk</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>onthebeach644@gmail.com</t>
+          <t>nancy.sukornyk@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Phil</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Moldaver</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>maureen.reisch@gmail.com</t>
+          <t>phil.adams111@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Shavaughn</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Soraine</t>
+          <t>Mosienko</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>shavaughn.soraine@gmail.com</t>
+          <t>lori.mosienko@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUMMERS</t>
+          <t>Redhead</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>adamsummerspt@gmail.com</t>
+          <t>sredhead1967@yahoo.ca</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Whalen</t>
+          <t>Walker</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>karenwhalen1955@gmail.com</t>
+          <t>sabrina.kim.walker@gmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jennelle</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cullen</t>
+          <t>Stefanski</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jcullen@compasselc.com</t>
+          <t>stefanskilisa@gmail.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Lynne</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Foden</t>
+          <t>Vautour</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>slfoden@icloud.com</t>
+          <t>vautour.lyn@gmail.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2107,17 +2107,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Clem</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Crowley</t>
+          <t>Garvey</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>albertzitacrowley@gmail.com</t>
+          <t>beleaf62@gmail.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2129,17 +2129,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>scott</t>
+          <t>Deanne</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>laing</t>
+          <t>Graham</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>buster6150@hotmail.com</t>
+          <t>deanne_graham@live.ca</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2151,17 +2151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Marlene</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Baillie</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>shar.kell.clar@gmail.com</t>
+          <t>marlenebaillie@gmail.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2173,17 +2173,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>WENDY</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mcmaster</t>
+          <t>Couper</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>cathymcmaster58@gmail.com</t>
+          <t>wendycouper@gmail.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2195,17 +2195,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kimber</t>
+          <t>Robin</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Kayser</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>bkbell94@yahoo.com</t>
+          <t>rkayser1010@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rachele</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Corso</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>rachelebell96@gmail.com</t>
+          <t>heathercorso@gmail.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Corinne</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Titus</t>
+          <t>Jenden-Selway</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>99silverado@sympatico.ca</t>
+          <t>jendenselwayca@aol.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,17 +2261,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tsafaridis</t>
+          <t>Fellion</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>safarimag69@gmail.com</t>
+          <t>heatherfellion@gmail.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2283,17 +2283,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Cheryl</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Greenfield</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>melanie.greenfield8@gmail.com</t>
+          <t>cherylchristie44@gmail.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2305,17 +2305,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Catherine</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Fulcher</t>
+          <t>Szabolcs</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>kim9fulcher@gmail.com</t>
+          <t>cathyszab@gmail.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Dhruv</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bolton</t>
+          <t>Mittal</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>tinaebolton@gmail.com</t>
+          <t>mittaldhruv99@gmail.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2349,17 +2349,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Denisa</t>
+          <t>Sadaf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reiz</t>
+          <t>Hussain</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>adeelight779@gmail.com</t>
+          <t>sadaf18@gmail.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2371,17 +2371,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Carmelina</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tamburini</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>carmelinaeliseo@hotmail.com</t>
+          <t>brittany_avon@ymail.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2393,17 +2393,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Zaa</t>
+          <t>Kylie</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nkweta</t>
+          <t>Morrison</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>nkwetaz@gmail.com</t>
+          <t>kylierosemorrison@gmail.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2415,17 +2415,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tracey</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Manns</t>
+          <t>Merpaw</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>tracey.manns@gmail.com</t>
+          <t>merpaw483@bell.net</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2437,17 +2437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Aditya</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Girdhar</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>girdhar0820@gmail.com</t>
+          <t>spacebuffalo1@gmail.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2459,20 +2459,1230 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>katie.wright1954@gmail.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jimenez santamaria</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>angelicapmp@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Duggan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>stephduggan55@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Micks</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>micksfamily5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MacDowall</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dheliam26@icloud.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Pamela</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Chamberlain</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>pamelachamberlain12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Shannon</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>shannonkelly@live.ca</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hunt</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>rjd4hunt@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Jordyn</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GEROLAMY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>j_gerolamy@live.ca</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Hawksworth</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ladydihawk@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>tomtaylor74367@gmail.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Kristin</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Clark</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>kclark230@hmail.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sonya</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Hardman</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sonyahardman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>King</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>onthebeach644@gmail.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Maureen</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Moldaver</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>maureen.reisch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Shavaughn</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Soraine</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>shavaughn.soraine@gmail.com</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ADAM</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SUMMERS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>adamsummerspt@gmail.com</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Whalen</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>karenwhalen1955@gmail.com</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Jennelle</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cullen</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jcullen@compasselc.com</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Foden</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>slfoden@icloud.com</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Albert</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Crowley</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>albertzitacrowley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>scott</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>laing</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>buster6150@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sharon</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>shar.kell.clar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Cathy</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Mcmaster</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>cathymcmaster58@gmail.com</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kimber</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Bell</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>bkbell94@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Rachele</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Bell</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>rachelebell96@gmail.com</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Titus</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>99silverado@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Tsafaridis</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>safarimag69@gmail.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Melanie</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Greenfield</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>melanie.greenfield8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fulcher</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>kim9fulcher@gmail.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tina</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Bolton</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>tinaebolton@gmail.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Denisa</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Reiz</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>adeelight779@gmail.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Carmelina</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Tamburini</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>carmelinaeliseo@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Zaa</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Nkweta</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>nkwetaz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Tracey</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Manns</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>tracey.manns@gmail.com</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Aditya</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Girdhar</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>girdhar0820@gmail.com</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Madelyne</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Raja</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>madelyneraja@gmail.com</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Horner</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>dianehorner911@gmail.com</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Judy</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Wannop</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jbwannop@gmail.com</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>jrb.brown@gmail.com</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Quenum</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>eric.cadnel@gmail.com</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Mathers</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>mast1@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Allan</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>lindaspicesgoodfood@gmail.com</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Rachel</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Kenworthy</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>rachel.kenworthy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Cyndy</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Manol</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>cmanol@cogeco.ca</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>O'Sullivan</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>osullivanjack2010@gmail.com</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ratcliff</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>andrewratcliff44@gmail.com</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Susan</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Lang</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>jeff.susan@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Ezra Sage</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Agraan</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ezr2sage@gmail.com</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Alcock</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>lacock@gmail.com</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Shirley</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Bacigalupo</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>shirleybaci@gmail.com</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>O'Sullivan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>osullivanjack2010@gnail.com</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Joan</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>tomjoanjenjeff@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Debbie</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Giroux</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>debgiroux8@gmail.com</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Ty</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>t.bailz1253@gmail.com</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>peterborough@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Duncan</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Cowie</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>dhcowie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
         <is>
           <t>peterborough@pickleplex.ca</t>
         </is>
